--- a/reports/一级子公司B_利润表_2025-10.xlsx
+++ b/reports/一级子公司B_利润表_2025-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>50520617</v>
+        <v>67129155</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14887229</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>144163120</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>211154</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>2034289</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>189760</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>1830965</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>157790</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1525573</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>146903</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1423395</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>83744</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>812998</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>62691</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>609443</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>50520617</v>
+        <v>66277113</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>14035187</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8359958</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>81183690</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1256405</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>12178309</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>629725</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>6090736</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4208635</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>40621633</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>421759</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>4064159</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>316758</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>3049595</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>528147</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>5084649</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>422247</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>4068658</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>50440836</v>
+        <v>50589844</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>487701548</v>
+        <v>488253298</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>79781</v>
+        <v>80122</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>799969</v>
+        <v>800828</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>944060</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9149894</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>627900</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6097087</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>46407474</v>
+        <v>59688430</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26314176</v>
+        <v>33646931</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>158284</v>
+        <v>7516486</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1523965</v>
+        <v>73073782</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26155892</v>
+        <v>26130445</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>254008573</v>
+        <v>253698040</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1570981</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>15223247</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>503950</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4872819</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>315746</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3046813</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>379672</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3657988</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>285115</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2744797</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>190128</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1830549</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>158317</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1525772</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1266661</v>
+        <v>1264408</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>12191773</v>
+        <v>12206186</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>41830</v>
+        <v>42050</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>406413</v>
+        <v>406790</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2631168</v>
+        <v>2621520</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>25398995</v>
+        <v>25414924</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>15743919</v>
+        <v>15693154</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>152406695</v>
+        <v>152417029</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2611199</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>25390252</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>451550</v>
+        <v>447309</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4500170</v>
+        <v>4495729</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398049</v>
+        <v>397739</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3999889</v>
+        <v>3995088</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30173</v>
+        <v>29870</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>300005</v>
+        <v>299614</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134697</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1348480</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>275690</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2664955</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>90241</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>899760</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67813</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>675185</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>113152</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1125870</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>396083</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3813789</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>60301</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>600776</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45145</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>450550</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>75064</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>750705</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52413</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>525258</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37355</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>374984</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>29838</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>299831</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22365</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>224775</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>4113143</v>
+        <v>7545701</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-120333</v>
+        <v>4724824</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>157197</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1522414</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37522</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>374737</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>60319</v>
+        <v>60178</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>600014</v>
+        <v>599883</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>4052824</v>
+        <v>7642720</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1810600</v>
+        <v>1810569</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>17999901</v>
+        <v>18014939</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2242224</v>
+        <v>5832151</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2242224</v>
+        <v>5832151</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>2242224</v>
+        <v>5832151</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2242224</v>
+        <v>5832151</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2242224</v>
+        <v>5832151</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
